--- a/annual/Predicted_Annual_Jevons_Index_Results.xlsx
+++ b/annual/Predicted_Annual_Jevons_Index_Results.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet name="Predicted_Prices" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Adjacent Predicted Years" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Model_Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Summary" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6319,6 +6320,161 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Samples</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>R2_Score</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Features_Selected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>24</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.7210931761793971</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.02003603737161055</v>
+      </c>
+      <c r="E2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>47</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.8737106907869662</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.002141572161413451</v>
+      </c>
+      <c r="E3" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>86</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.5427145648829101</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.01224689212182456</v>
+      </c>
+      <c r="E4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>118</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.5687588702336235</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.005696889564220076</v>
+      </c>
+      <c r="E5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>142</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.5598213470275615</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.003692674452339327</v>
+      </c>
+      <c r="E6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>148</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.5319062406653978</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.004409237039954232</v>
+      </c>
+      <c r="E7" t="n">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/annual/Predicted_Annual_Jevons_Index_Results.xlsx
+++ b/annual/Predicted_Annual_Jevons_Index_Results.xlsx
@@ -10,7 +10,8 @@
     <sheet name="Predicted_Prices" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Adjacent Predicted Years" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Model_Summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Summary" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Coefficients" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Summary" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6475,6 +6476,1348 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Coefficient</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Abs_Coefficient</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>CI_Lower</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>CI_Upper</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>is_ios</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.294637528490902</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>mobile_weight_numeric</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.005367861904664423</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.005367861904664423</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.05050917923634255</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.08576249042728458</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ram_mem_numeric</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.03865877825646851</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>front_camera_mp</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.09274109307751709</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1821570366114603</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>max_mp_numeric</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.02054510313042503</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.02054510313042503</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.3532954720715814</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1014380118534539</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>num_cameras_numeric</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.1895196342748185</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.1895196342748185</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.0727405490281807</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.275753861322425</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>processor_level_encoded</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>battery_capacity_numeric</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.07832322542219847</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.07832322542219847</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-0.03398436562520878</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.3201802665142452</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>screen_size_numeric</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.0783302733726048</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>is_ios</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.9951651338714587</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.9951651338714587</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.63199842647655</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.533767722411089</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>mobile_weight_numeric</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.4431005896535805</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.4431005896535805</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-0.859130259662056</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.1091657218740165</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ram_mem_numeric</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.4599297324350201</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.4599297324350201</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.3094717909155534</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.6863999302985907</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>front_camera_mp</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.07782040350957277</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.07782040350957277</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-0.03141246695333853</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.2536002131524199</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>max_mp_numeric</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0.1517769323382573</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.1517769323382573</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0.3110478873376593</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.3026534517279693</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>num_cameras_numeric</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.2219831846552474</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.2219831846552474</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.09052966441942541</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.3740762331274841</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>processor_level_encoded</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-0.1379684794643573</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.1731586233857189</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>battery_capacity_numeric</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.2584895673798991</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.2584895673798991</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.1168861926943545</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.6329195097413227</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>screen_size_numeric</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.2333211655735792</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.2333211655735792</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.06011476413954368</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.5916044447253503</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>is_ios</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.511281908734335</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.511281908734335</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.4264507524925135</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.7901967476334476</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>mobile_weight_numeric</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.01251377171361233</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.01251377171361233</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-0.1899613985369172</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.2007325462191218</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ram_mem_numeric</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0.3538248028668088</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.3538248028668088</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.2363500052932929</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.6020417554612216</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>front_camera_mp</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0.03069143535638131</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.03069143535638131</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-0.04132458998915348</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.145507914355013</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>max_mp_numeric</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.02062385774308309</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.02062385774308309</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-0.1150268382434964</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.1220703697846265</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>num_cameras_numeric</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.007140991240328554</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.007140991240328554</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-0.08801569291443855</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.1233031769331877</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>processor_level_encoded</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.1084870011272918</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.1084870011272918</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.2377842013587159</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>battery_capacity_numeric</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.1206882616941224</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.1206882616941224</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.4233469844163077</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>screen_size_numeric</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-0.2717441705932908</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.07706873732039865</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>is_ios</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.4879001603524376</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.4879001603524376</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.4192967310025927</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.6395520038161887</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>mobile_weight_numeric</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.09264260960913891</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.09264260960913891</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-0.06180366987281007</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.2012840722016914</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ram_mem_numeric</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.3858501651900217</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.3858501651900217</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.2644853221403639</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.5369883676290591</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>front_camera_mp</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.1274714142871125</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.1274714142871125</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.01913051935934279</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.2414946414854251</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>max_mp_numeric</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.02668406540493391</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.02668406540493391</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-0.08532110257858509</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.1442653174501556</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>num_cameras_numeric</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>-0.07179258231342424</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.07179258231342424</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-0.1445780667319641</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>processor_level_encoded</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.02248346262736626</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.02248346262736626</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-0.06062933509438955</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.1258278629486903</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>battery_capacity_numeric</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-0.1215941307542096</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.1524310221967258</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>screen_size_numeric</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.03419906429037019</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.03419906429037019</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-0.08141232003539507</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.2087000670556607</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>is_ios</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.5085873451469313</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.5085873451469313</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.4091863049828602</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.671234492582499</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>mobile_weight_numeric</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.04719100126368755</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.04719100126368755</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-0.1156333881817467</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.1591674531967267</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ram_mem_numeric</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.3916993092574511</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.3916993092574511</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.2554488866893505</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.534168172327565</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>front_camera_mp</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.1432828259081212</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.1432828259081212</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.02942471726233167</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.2639369836648443</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>max_mp_numeric</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.05676538103905797</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.05676538103905797</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-0.04341827610220937</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.2018650178628935</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>num_cameras_numeric</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>-0.09931722530273769</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.09931722530273769</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-0.1811821620139592</v>
+      </c>
+      <c r="F43" t="n">
+        <v>-0.01037771000781747</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>processor_level_encoded</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>-0.03409618458806112</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.03409618458806112</v>
+      </c>
+      <c r="E44" t="n">
+        <v>-0.1294374454323508</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.05225837642489271</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>battery_capacity_numeric</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.08733925708239269</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.08733925708239269</v>
+      </c>
+      <c r="E45" t="n">
+        <v>-0.03753100488213649</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.2599006249129768</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>screen_size_numeric</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.007070455873215417</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.007070455873215417</v>
+      </c>
+      <c r="E46" t="n">
+        <v>-0.1222240313373687</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.1663373149738913</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>is_ios</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.4442832527289372</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.4442832527289372</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.3482886922916187</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.6390284421930539</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>mobile_weight_numeric</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="n">
+        <v>-0.1705593885610894</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.1199964757922218</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ram_mem_numeric</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.3856713881442079</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.3856713881442079</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.2673581781987348</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.5454489362947884</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>front_camera_mp</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.1427863229175846</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.1427863229175846</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.04271548836172004</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.2728272445682664</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>max_mp_numeric</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0.05746331247405263</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.05746331247405263</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-0.02711411704056076</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.1816973636457519</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>num_cameras_numeric</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>-0.06436851543307254</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.06436851543307254</v>
+      </c>
+      <c r="E52" t="n">
+        <v>-0.1449893335131352</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.005390195178873186</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>processor_level_encoded</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>-0.05653136243502357</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.05653136243502357</v>
+      </c>
+      <c r="E53" t="n">
+        <v>-0.1534003024813351</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.01193646138706785</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>battery_capacity_numeric</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0.1073815907247067</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.1073815907247067</v>
+      </c>
+      <c r="E54" t="n">
+        <v>-0.003986775363099902</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.2798269639559106</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>screen_size_numeric</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0.03817352289150102</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.03817352289150102</v>
+      </c>
+      <c r="E55" t="n">
+        <v>-0.106868508515233</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.248064453531306</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/annual/Predicted_Annual_Jevons_Index_Results.xlsx
+++ b/annual/Predicted_Annual_Jevons_Index_Results.xlsx
@@ -10,8 +10,9 @@
     <sheet name="Predicted_Prices" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Adjacent Predicted Years" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Model_Summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Coefficients" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Price_Change_R2" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Coefficients" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Summary" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6476,1335 +6477,102 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Year</t>
+          <t>Period</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>R2_Price_Change</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Coefficient</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Abs_Coefficient</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>CI_Lower</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>CI_Upper</t>
+          <t>Samples</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>is_ios</t>
-        </is>
+          <t>2020 → 2021</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.2167166496047672</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.294637528490902</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>mobile_weight_numeric</t>
-        </is>
+          <t>2021 → 2022</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.2455885598980011</v>
       </c>
       <c r="C3" t="n">
-        <v>0.005367861904664423</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.005367861904664423</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-0.05050917923634255</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.08576249042728458</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ram_mem_numeric</t>
-        </is>
+          <t>2022 → 2023</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.1609001378411616</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.03865877825646851</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>front_camera_mp</t>
-        </is>
+          <t>2023 → 2024</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.1251226965480657</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-0.09274109307751709</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.1821570366114603</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>max_mp_numeric</t>
-        </is>
+          <t>2024 → 2025</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.2092079379524306</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02054510313042503</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.02054510313042503</v>
-      </c>
-      <c r="E6" t="n">
-        <v>-0.3532954720715814</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.1014380118534539</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>num_cameras_numeric</t>
-        </is>
+          <t>Overall (Average)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.1915071963688853</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1895196342748185</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.1895196342748185</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.0727405490281807</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.275753861322425</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>processor_level_encoded</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>battery_capacity_numeric</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>0.07832322542219847</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.07832322542219847</v>
-      </c>
-      <c r="E9" t="n">
-        <v>-0.03398436562520878</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.3201802665142452</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>screen_size_numeric</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.0783302733726048</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>is_ios</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>0.9951651338714587</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.9951651338714587</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.63199842647655</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1.533767722411089</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>mobile_weight_numeric</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>-0.4431005896535805</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.4431005896535805</v>
-      </c>
-      <c r="E12" t="n">
-        <v>-0.859130259662056</v>
-      </c>
-      <c r="F12" t="n">
-        <v>-0.1091657218740165</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>ram_mem_numeric</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>0.4599297324350201</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.4599297324350201</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.3094717909155534</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.6863999302985907</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>front_camera_mp</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>0.07782040350957277</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.07782040350957277</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.03141246695333853</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.2536002131524199</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>max_mp_numeric</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>0.1517769323382573</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.1517769323382573</v>
-      </c>
-      <c r="E15" t="n">
-        <v>-0.3110478873376593</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.3026534517279693</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>num_cameras_numeric</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>0.2219831846552474</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.2219831846552474</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.09052966441942541</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.3740762331274841</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>processor_level_encoded</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>-0.1379684794643573</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.1731586233857189</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>battery_capacity_numeric</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>0.2584895673798991</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.2584895673798991</v>
-      </c>
-      <c r="E18" t="n">
-        <v>-0.1168861926943545</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.6329195097413227</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>screen_size_numeric</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>0.2333211655735792</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.2333211655735792</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.06011476413954368</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.5916044447253503</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>is_ios</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>0.511281908734335</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.511281908734335</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.4264507524925135</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.7901967476334476</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>mobile_weight_numeric</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>0.01251377171361233</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.01251377171361233</v>
-      </c>
-      <c r="E21" t="n">
-        <v>-0.1899613985369172</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.2007325462191218</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>ram_mem_numeric</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>0.3538248028668088</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.3538248028668088</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.2363500052932929</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.6020417554612216</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>front_camera_mp</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>0.03069143535638131</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0.03069143535638131</v>
-      </c>
-      <c r="E23" t="n">
-        <v>-0.04132458998915348</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.145507914355013</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>max_mp_numeric</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>0.02062385774308309</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.02062385774308309</v>
-      </c>
-      <c r="E24" t="n">
-        <v>-0.1150268382434964</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.1220703697846265</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>num_cameras_numeric</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>0.007140991240328554</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.007140991240328554</v>
-      </c>
-      <c r="E25" t="n">
-        <v>-0.08801569291443855</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.1233031769331877</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>processor_level_encoded</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>0.1084870011272918</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0.1084870011272918</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.2377842013587159</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>battery_capacity_numeric</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>0.1206882616941224</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0.1206882616941224</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.4233469844163077</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>screen_size_numeric</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="n">
-        <v>-0.2717441705932908</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.07706873732039865</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>is_ios</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>0.4879001603524376</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0.4879001603524376</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.4192967310025927</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.6395520038161887</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>mobile_weight_numeric</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>0.09264260960913891</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.09264260960913891</v>
-      </c>
-      <c r="E30" t="n">
-        <v>-0.06180366987281007</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.2012840722016914</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>ram_mem_numeric</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>0.3858501651900217</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.3858501651900217</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0.2644853221403639</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0.5369883676290591</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>front_camera_mp</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>0.1274714142871125</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0.1274714142871125</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.01913051935934279</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0.2414946414854251</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>max_mp_numeric</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>0.02668406540493391</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0.02668406540493391</v>
-      </c>
-      <c r="E33" t="n">
-        <v>-0.08532110257858509</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0.1442653174501556</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>num_cameras_numeric</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>-0.07179258231342424</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0.07179258231342424</v>
-      </c>
-      <c r="E34" t="n">
-        <v>-0.1445780667319641</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>processor_level_encoded</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>0.02248346262736626</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0.02248346262736626</v>
-      </c>
-      <c r="E35" t="n">
-        <v>-0.06062933509438955</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.1258278629486903</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>battery_capacity_numeric</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" t="n">
-        <v>-0.1215941307542096</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.1524310221967258</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>screen_size_numeric</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>0.03419906429037019</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0.03419906429037019</v>
-      </c>
-      <c r="E37" t="n">
-        <v>-0.08141232003539507</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.2087000670556607</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>is_ios</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>0.5085873451469313</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0.5085873451469313</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0.4091863049828602</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.671234492582499</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>mobile_weight_numeric</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>0.04719100126368755</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0.04719100126368755</v>
-      </c>
-      <c r="E39" t="n">
-        <v>-0.1156333881817467</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.1591674531967267</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>ram_mem_numeric</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>0.3916993092574511</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0.3916993092574511</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0.2554488866893505</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.534168172327565</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>front_camera_mp</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>0.1432828259081212</v>
-      </c>
-      <c r="D41" t="n">
-        <v>0.1432828259081212</v>
-      </c>
-      <c r="E41" t="n">
-        <v>0.02942471726233167</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0.2639369836648443</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>max_mp_numeric</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>0.05676538103905797</v>
-      </c>
-      <c r="D42" t="n">
-        <v>0.05676538103905797</v>
-      </c>
-      <c r="E42" t="n">
-        <v>-0.04341827610220937</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0.2018650178628935</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>num_cameras_numeric</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>-0.09931722530273769</v>
-      </c>
-      <c r="D43" t="n">
-        <v>0.09931722530273769</v>
-      </c>
-      <c r="E43" t="n">
-        <v>-0.1811821620139592</v>
-      </c>
-      <c r="F43" t="n">
-        <v>-0.01037771000781747</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>processor_level_encoded</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>-0.03409618458806112</v>
-      </c>
-      <c r="D44" t="n">
-        <v>0.03409618458806112</v>
-      </c>
-      <c r="E44" t="n">
-        <v>-0.1294374454323508</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0.05225837642489271</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>battery_capacity_numeric</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>0.08733925708239269</v>
-      </c>
-      <c r="D45" t="n">
-        <v>0.08733925708239269</v>
-      </c>
-      <c r="E45" t="n">
-        <v>-0.03753100488213649</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0.2599006249129768</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>screen_size_numeric</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>0.007070455873215417</v>
-      </c>
-      <c r="D46" t="n">
-        <v>0.007070455873215417</v>
-      </c>
-      <c r="E46" t="n">
-        <v>-0.1222240313373687</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0.1663373149738913</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>is_ios</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>0.4442832527289372</v>
-      </c>
-      <c r="D47" t="n">
-        <v>0.4442832527289372</v>
-      </c>
-      <c r="E47" t="n">
-        <v>0.3482886922916187</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0.6390284421930539</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>mobile_weight_numeric</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" t="n">
-        <v>-0.1705593885610894</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0.1199964757922218</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>ram_mem_numeric</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>0.3856713881442079</v>
-      </c>
-      <c r="D49" t="n">
-        <v>0.3856713881442079</v>
-      </c>
-      <c r="E49" t="n">
-        <v>0.2673581781987348</v>
-      </c>
-      <c r="F49" t="n">
-        <v>0.5454489362947884</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>front_camera_mp</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>0.1427863229175846</v>
-      </c>
-      <c r="D50" t="n">
-        <v>0.1427863229175846</v>
-      </c>
-      <c r="E50" t="n">
-        <v>0.04271548836172004</v>
-      </c>
-      <c r="F50" t="n">
-        <v>0.2728272445682664</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>max_mp_numeric</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>0.05746331247405263</v>
-      </c>
-      <c r="D51" t="n">
-        <v>0.05746331247405263</v>
-      </c>
-      <c r="E51" t="n">
-        <v>-0.02711411704056076</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0.1816973636457519</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>num_cameras_numeric</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>-0.06436851543307254</v>
-      </c>
-      <c r="D52" t="n">
-        <v>0.06436851543307254</v>
-      </c>
-      <c r="E52" t="n">
-        <v>-0.1449893335131352</v>
-      </c>
-      <c r="F52" t="n">
-        <v>0.005390195178873186</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>processor_level_encoded</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>-0.05653136243502357</v>
-      </c>
-      <c r="D53" t="n">
-        <v>0.05653136243502357</v>
-      </c>
-      <c r="E53" t="n">
-        <v>-0.1534003024813351</v>
-      </c>
-      <c r="F53" t="n">
-        <v>0.01193646138706785</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>battery_capacity_numeric</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>0.1073815907247067</v>
-      </c>
-      <c r="D54" t="n">
-        <v>0.1073815907247067</v>
-      </c>
-      <c r="E54" t="n">
-        <v>-0.003986775363099902</v>
-      </c>
-      <c r="F54" t="n">
-        <v>0.2798269639559106</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>screen_size_numeric</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>0.03817352289150102</v>
-      </c>
-      <c r="D55" t="n">
-        <v>0.03817352289150102</v>
-      </c>
-      <c r="E55" t="n">
-        <v>-0.106868508515233</v>
-      </c>
-      <c r="F55" t="n">
-        <v>0.248064453531306</v>
+        <v>413</v>
       </c>
     </row>
   </sheetData>
@@ -7818,6 +6586,1348 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Coefficient</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Abs_Coefficient</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>CI_Lower</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>CI_Upper</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>is_ios</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.294637528490902</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>mobile_weight_numeric</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.005367861904664423</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.005367861904664423</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.05050917923634255</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.08576249042728458</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ram_mem_numeric</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.03865877825646851</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>front_camera_mp</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.09274109307751709</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1821570366114603</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>max_mp_numeric</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.02054510313042503</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.02054510313042503</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.3532954720715814</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1014380118534539</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>num_cameras_numeric</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.1895196342748185</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.1895196342748185</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.0727405490281807</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.275753861322425</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>processor_level_encoded</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>battery_capacity_numeric</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.07832322542219847</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.07832322542219847</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-0.03398436562520878</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.3201802665142452</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>screen_size_numeric</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.0783302733726048</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>is_ios</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.9951651338714587</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.9951651338714587</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.63199842647655</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.533767722411089</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>mobile_weight_numeric</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.4431005896535805</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.4431005896535805</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-0.859130259662056</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.1091657218740165</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ram_mem_numeric</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.4599297324350201</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.4599297324350201</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.3094717909155534</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.6863999302985907</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>front_camera_mp</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.07782040350957277</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.07782040350957277</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-0.03141246695333853</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.2536002131524199</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>max_mp_numeric</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0.1517769323382573</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.1517769323382573</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0.3110478873376593</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.3026534517279693</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>num_cameras_numeric</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.2219831846552474</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.2219831846552474</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.09052966441942541</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.3740762331274841</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>processor_level_encoded</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-0.1379684794643573</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.1731586233857189</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>battery_capacity_numeric</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.2584895673798991</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.2584895673798991</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.1168861926943545</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.6329195097413227</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>screen_size_numeric</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.2333211655735792</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.2333211655735792</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.06011476413954368</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.5916044447253503</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>is_ios</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.511281908734335</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.511281908734335</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.4264507524925135</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.7901967476334476</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>mobile_weight_numeric</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.01251377171361233</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.01251377171361233</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-0.1899613985369172</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.2007325462191218</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ram_mem_numeric</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0.3538248028668088</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.3538248028668088</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.2363500052932929</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.6020417554612216</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>front_camera_mp</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0.03069143535638131</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.03069143535638131</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-0.04132458998915348</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.145507914355013</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>max_mp_numeric</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.02062385774308309</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.02062385774308309</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-0.1150268382434964</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.1220703697846265</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>num_cameras_numeric</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.007140991240328554</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.007140991240328554</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-0.08801569291443855</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.1233031769331877</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>processor_level_encoded</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.1084870011272918</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.1084870011272918</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.2377842013587159</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>battery_capacity_numeric</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.1206882616941224</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.1206882616941224</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.4233469844163077</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>screen_size_numeric</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-0.2717441705932908</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.07706873732039865</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>is_ios</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.4879001603524376</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.4879001603524376</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.4192967310025927</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.6395520038161887</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>mobile_weight_numeric</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.09264260960913891</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.09264260960913891</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-0.06180366987281007</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.2012840722016914</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ram_mem_numeric</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.3858501651900217</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.3858501651900217</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.2644853221403639</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.5369883676290591</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>front_camera_mp</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.1274714142871125</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.1274714142871125</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.01913051935934279</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.2414946414854251</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>max_mp_numeric</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.02668406540493391</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.02668406540493391</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-0.08532110257858509</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.1442653174501556</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>num_cameras_numeric</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>-0.07179258231342424</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.07179258231342424</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-0.1445780667319641</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>processor_level_encoded</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.02248346262736626</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.02248346262736626</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-0.06062933509438955</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.1258278629486903</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>battery_capacity_numeric</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-0.1215941307542096</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.1524310221967258</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>screen_size_numeric</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.03419906429037019</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.03419906429037019</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-0.08141232003539507</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.2087000670556607</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>is_ios</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.5085873451469313</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.5085873451469313</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.4091863049828602</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.671234492582499</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>mobile_weight_numeric</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.04719100126368755</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.04719100126368755</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-0.1156333881817467</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.1591674531967267</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ram_mem_numeric</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.3916993092574511</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.3916993092574511</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.2554488866893505</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.534168172327565</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>front_camera_mp</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.1432828259081212</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.1432828259081212</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.02942471726233167</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.2639369836648443</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>max_mp_numeric</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.05676538103905797</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.05676538103905797</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-0.04341827610220937</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.2018650178628935</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>num_cameras_numeric</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>-0.09931722530273769</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.09931722530273769</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-0.1811821620139592</v>
+      </c>
+      <c r="F43" t="n">
+        <v>-0.01037771000781747</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>processor_level_encoded</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>-0.03409618458806112</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.03409618458806112</v>
+      </c>
+      <c r="E44" t="n">
+        <v>-0.1294374454323508</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.05225837642489271</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>battery_capacity_numeric</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.08733925708239269</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.08733925708239269</v>
+      </c>
+      <c r="E45" t="n">
+        <v>-0.03753100488213649</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.2599006249129768</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>screen_size_numeric</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.007070455873215417</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.007070455873215417</v>
+      </c>
+      <c r="E46" t="n">
+        <v>-0.1222240313373687</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.1663373149738913</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>is_ios</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.4442832527289372</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.4442832527289372</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.3482886922916187</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.6390284421930539</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>mobile_weight_numeric</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="n">
+        <v>-0.1705593885610894</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.1199964757922218</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ram_mem_numeric</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.3856713881442079</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.3856713881442079</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.2673581781987348</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.5454489362947884</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>front_camera_mp</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.1427863229175846</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.1427863229175846</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.04271548836172004</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.2728272445682664</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>max_mp_numeric</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0.05746331247405263</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.05746331247405263</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-0.02711411704056076</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.1816973636457519</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>num_cameras_numeric</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>-0.06436851543307254</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.06436851543307254</v>
+      </c>
+      <c r="E52" t="n">
+        <v>-0.1449893335131352</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.005390195178873186</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>processor_level_encoded</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>-0.05653136243502357</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.05653136243502357</v>
+      </c>
+      <c r="E53" t="n">
+        <v>-0.1534003024813351</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.01193646138706785</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>battery_capacity_numeric</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0.1073815907247067</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.1073815907247067</v>
+      </c>
+      <c r="E54" t="n">
+        <v>-0.003986775363099902</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.2798269639559106</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>screen_size_numeric</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0.03817352289150102</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.03817352289150102</v>
+      </c>
+      <c r="E55" t="n">
+        <v>-0.106868508515233</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.248064453531306</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
